--- a/WH Cost/WH cost.xlsx
+++ b/WH Cost/WH cost.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t>Own</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Export Truck times</t>
   </si>
   <si>
-    <t>测试</t>
-  </si>
-  <si>
     <t>WH type</t>
   </si>
   <si>
@@ -168,12 +165,6 @@
   </si>
   <si>
     <t>Export</t>
-  </si>
-  <si>
-    <t>kk</t>
-  </si>
-  <si>
-    <t>dd</t>
   </si>
 </sst>
 </file>
@@ -187,14 +178,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -363,7 +347,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399914548173467"/>
+        <fgColor theme="4" tint="0.399884029663991"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -714,167 +698,164 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="2" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="2" borderId="2" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="49" applyBorder="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1188,73 +1169,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z9"/>
-  <sheetFormatPr defaultColWidth="9.45454545454546" defaultRowHeight="14"/>
+  <dimension ref="A1:Y7"/>
+  <sheetFormatPr defaultColWidth="9.45454545454546" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="9.63636363636364" style="2" customWidth="1"/>
     <col min="2" max="2" width="7.09090909090909" style="2" customWidth="1"/>
     <col min="3" max="3" width="8.36363636363636" style="2" customWidth="1"/>
     <col min="4" max="4" width="10.9090909090909" style="2" customWidth="1"/>
     <col min="5" max="5" width="12.3636363636364" style="2" customWidth="1"/>
-    <col min="6" max="8" width="10.6363636363636" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.4545454545455" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.36363636363636" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.0909090909091" style="3" customWidth="1"/>
-    <col min="12" max="12" width="8.36363636363636" style="2" customWidth="1"/>
-    <col min="13" max="13" width="23.1818181818182" style="4" customWidth="1"/>
-    <col min="14" max="14" width="23.1818181818182" style="2" customWidth="1"/>
-    <col min="15" max="15" width="18.8181818181818" style="2" customWidth="1"/>
-    <col min="16" max="16" width="17" style="2" customWidth="1"/>
-    <col min="17" max="17" width="29.2727272727273" style="2" customWidth="1"/>
-    <col min="18" max="18" width="29" style="2" customWidth="1"/>
-    <col min="19" max="19" width="18.9090909090909" style="2" customWidth="1"/>
-    <col min="20" max="21" width="13.6363636363636" style="2" customWidth="1"/>
-    <col min="22" max="22" width="16.0909090909091" style="2" customWidth="1"/>
-    <col min="23" max="24" width="18.2727272727273" style="2" customWidth="1"/>
-    <col min="25" max="25" width="31.4545454545455" style="2" customWidth="1"/>
-    <col min="26" max="26" width="21.3636363636364" style="2" customWidth="1"/>
-    <col min="27" max="16384" width="9.45454545454546" style="2"/>
+    <col min="6" max="7" width="10.6363636363636" style="2" customWidth="1"/>
+    <col min="8" max="8" width="10.4545454545455" style="2" customWidth="1"/>
+    <col min="9" max="9" width="5.36363636363636" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.0909090909091" style="3" customWidth="1"/>
+    <col min="11" max="11" width="8.36363636363636" style="2" customWidth="1"/>
+    <col min="12" max="12" width="23.1818181818182" style="4" customWidth="1"/>
+    <col min="13" max="13" width="23.1818181818182" style="2" customWidth="1"/>
+    <col min="14" max="14" width="18.8181818181818" style="2" customWidth="1"/>
+    <col min="15" max="15" width="17" style="2" customWidth="1"/>
+    <col min="16" max="16" width="29.2727272727273" style="2" customWidth="1"/>
+    <col min="17" max="17" width="29" style="2" customWidth="1"/>
+    <col min="18" max="18" width="18.9090909090909" style="2" customWidth="1"/>
+    <col min="19" max="20" width="13.6363636363636" style="2" customWidth="1"/>
+    <col min="21" max="21" width="16.0909090909091" style="2" customWidth="1"/>
+    <col min="22" max="23" width="18.2727272727273" style="2" customWidth="1"/>
+    <col min="24" max="24" width="31.4545454545455" style="2" customWidth="1"/>
+    <col min="25" max="25" width="21.3636363636364" style="2" customWidth="1"/>
+    <col min="26" max="16384" width="9.45454545454546" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:25">
+      <c r="M1" s="2">
+        <v>1</v>
+      </c>
       <c r="N1" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O1" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P1" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q1" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R1" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S1" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T1" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U1" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V1" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W1" s="2">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="X1" s="2">
+        <v>12</v>
       </c>
       <c r="Y1" s="2">
-        <v>11</v>
-      </c>
-      <c r="Z1" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="42" spans="1:26">
+    <row r="2" s="1" customFormat="1" ht="42" spans="1:25">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1282,16 +1266,16 @@
       <c r="I2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>10</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="5" t="s">
         <v>12</v>
       </c>
       <c r="N2" s="5" t="s">
@@ -1330,13 +1314,10 @@
       <c r="Y2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="5" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" ht="28" spans="1:25">
+      <c r="A3" s="5" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="28" spans="1:26">
-      <c r="A3" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1346,11 +1327,13 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="8"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="7"/>
       <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7" t="s">
+      <c r="M3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>27</v>
       </c>
       <c r="O3" s="5" t="s">
@@ -1360,7 +1343,7 @@
         <v>29</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>30</v>
@@ -1369,7 +1352,7 @@
         <v>31</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="U3" s="5" t="s">
         <v>32</v>
@@ -1377,382 +1360,265 @@
       <c r="V3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="W3" s="5"/>
+      <c r="X3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="X3" s="5"/>
       <c r="Y3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="Z3" s="5" t="s">
+    </row>
+    <row r="4" spans="1:25">
+      <c r="A4" s="8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:26">
-      <c r="A4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="9">
+      <c r="E4" s="8">
         <v>8</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <v>8</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9">
+      <c r="G4" s="8"/>
+      <c r="H4" s="8">
         <v>300</v>
       </c>
+      <c r="I4" s="8">
+        <v>428.4</v>
+      </c>
       <c r="J4" s="9">
-        <v>428.4</v>
+        <f>(SUM(P4:V4)+K4*O4)*1.1</f>
+        <v>348080.04</v>
       </c>
       <c r="K4" s="10">
-        <f>(SUM(Q4:W4)+L4*P4)*1.1</f>
-        <v>348080.04</v>
+        <v>9</v>
       </c>
       <c r="L4" s="11">
-        <v>9</v>
-      </c>
-      <c r="M4" s="12">
         <v>25888195.7783333</v>
       </c>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="9">
-        <f>J4*2.3*30</f>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="8">
+        <f>I4*2.3*30</f>
         <v>29559.6</v>
       </c>
-      <c r="Q4" s="9">
+      <c r="P4" s="8">
         <f>350*E4</f>
         <v>2800</v>
       </c>
-      <c r="R4" s="9">
+      <c r="Q4" s="8">
         <f>350*F4</f>
         <v>2800</v>
       </c>
-      <c r="S4" s="9">
-        <f>30*I4</f>
+      <c r="R4" s="8">
+        <f>30*H4</f>
         <v>9000</v>
       </c>
-      <c r="T4" s="9">
-        <f>25*I4</f>
+      <c r="S4" s="8">
+        <f>25*H4</f>
         <v>7500</v>
       </c>
-      <c r="U4" s="9">
-        <f>25*I4</f>
+      <c r="T4" s="8">
+        <f>25*H4</f>
         <v>7500</v>
       </c>
-      <c r="V4" s="9">
+      <c r="U4" s="8">
         <f>900*E4</f>
         <v>7200</v>
       </c>
-      <c r="W4" s="9">
+      <c r="V4" s="8">
         <f>1700*F4</f>
         <v>13600</v>
       </c>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="9"/>
+      <c r="W4" s="8">
+        <v>99</v>
+      </c>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
     </row>
-    <row r="5" spans="1:26">
-      <c r="A5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="9" t="s">
+    <row r="5" spans="1:25">
+      <c r="A5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>8</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>8</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9">
+      <c r="G5" s="8"/>
+      <c r="H5" s="8">
         <v>300</v>
       </c>
+      <c r="I5" s="8">
+        <v>428.4</v>
+      </c>
       <c r="J5" s="9">
-        <v>428.4</v>
+        <f>(SUM(P5:Y5)+K5*O5)*1.1</f>
+        <v>547529.147493166</v>
       </c>
       <c r="K5" s="10">
-        <f>(SUM(Q5:Z5)+L5*P5)*1.1</f>
-        <v>547529.147493166</v>
+        <v>9</v>
       </c>
       <c r="L5" s="11">
-        <v>9</v>
-      </c>
-      <c r="M5" s="12">
         <v>25888195.7783333</v>
       </c>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="9">
-        <f>J5*2.3*30</f>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="8">
+        <f>I5*2.3*30</f>
         <v>29559.6</v>
       </c>
-      <c r="Q5" s="9">
+      <c r="P5" s="8">
         <f>350*E5</f>
         <v>2800</v>
       </c>
-      <c r="R5" s="9">
+      <c r="Q5" s="8">
         <f>350*F5</f>
         <v>2800</v>
       </c>
-      <c r="S5" s="9">
-        <f>30*I5</f>
+      <c r="R5" s="8">
+        <f>30*H5</f>
         <v>9000</v>
       </c>
-      <c r="T5" s="9">
-        <f>25*I5</f>
+      <c r="S5" s="8">
+        <f>25*H5</f>
         <v>7500</v>
       </c>
-      <c r="U5" s="9">
-        <f>25*I5</f>
+      <c r="T5" s="8">
+        <f>25*H5</f>
         <v>7500</v>
       </c>
-      <c r="V5" s="9">
+      <c r="U5" s="8">
         <f>900*E5</f>
         <v>7200</v>
       </c>
-      <c r="W5" s="9">
+      <c r="V5" s="8">
         <f>1700*F5</f>
         <v>13600</v>
       </c>
-      <c r="X5" s="9">
+      <c r="W5" s="8">
         <v>100</v>
       </c>
-      <c r="Y5" s="9">
-        <f>0.001*M5</f>
+      <c r="X5" s="8">
+        <f>0.001*L5</f>
         <v>25888.1957783333</v>
       </c>
-      <c r="Z5" s="9">
-        <f>0.006*M5</f>
+      <c r="Y5" s="8">
+        <f>0.006*L5</f>
         <v>155329.17467</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
-      <c r="A6" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="9" t="s">
+    <row r="6" spans="1:25">
+      <c r="A6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9">
-        <v>222</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="9">
+        <f>M6*K6</f>
+        <v>65000</v>
+      </c>
       <c r="K6" s="10">
-        <f>N6*L6</f>
-        <v>65000</v>
-      </c>
-      <c r="L6" s="11">
         <v>1</v>
       </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="11">
+      <c r="L6" s="11"/>
+      <c r="M6" s="10">
         <f>65000</f>
         <v>65000</v>
       </c>
-      <c r="O6" s="11"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8"/>
     </row>
-    <row r="7" spans="1:26">
-      <c r="A7" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="9" t="s">
+    <row r="7" spans="1:25">
+      <c r="A7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9">
-        <v>333</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" s="9">
+      <c r="D7" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="8">
         <v>10</v>
       </c>
+      <c r="I7" s="8">
+        <v>12</v>
+      </c>
       <c r="J7" s="9">
-        <v>12</v>
+        <f>N7*K7</f>
+        <v>5760</v>
       </c>
       <c r="K7" s="10">
-        <f t="shared" ref="K7:K9" si="0">O7*L7</f>
-        <v>5760</v>
-      </c>
-      <c r="L7" s="11">
         <v>2</v>
       </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11">
-        <f t="shared" ref="O7:O9" si="1">60*J7*4</f>
+      <c r="L7" s="11"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10">
+        <f>60*I7*4</f>
         <v>2880</v>
       </c>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
-    </row>
-    <row r="8" spans="1:26">
-      <c r="A8" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9">
-        <v>333</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="9">
-        <v>10</v>
-      </c>
-      <c r="J8" s="9">
-        <v>12</v>
-      </c>
-      <c r="K8" s="10">
-        <f t="shared" si="0"/>
-        <v>5760</v>
-      </c>
-      <c r="L8" s="11">
-        <v>2</v>
-      </c>
-      <c r="M8" s="12"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11">
-        <f t="shared" si="1"/>
-        <v>2880</v>
-      </c>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="9"/>
-      <c r="Z8" s="9"/>
-    </row>
-    <row r="9" spans="1:26">
-      <c r="A9" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="9">
-        <v>1</v>
-      </c>
-      <c r="F9" s="9">
-        <v>1</v>
-      </c>
-      <c r="G9" s="9">
-        <v>333</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="9">
-        <v>10</v>
-      </c>
-      <c r="J9" s="9">
-        <v>12</v>
-      </c>
-      <c r="K9" s="10">
-        <f t="shared" si="0"/>
-        <v>5760</v>
-      </c>
-      <c r="L9" s="11">
-        <v>2</v>
-      </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11">
-        <f t="shared" si="1"/>
-        <v>2880</v>
-      </c>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="9"/>
-      <c r="Z9" s="9"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
